--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/дв 25,08,26 днрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/дв 25,08,26 днрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\25,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C949C5-2BDD-4711-BF0E-B8BEA8DD8979}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2286D0ED-E772-4405-9C53-B5C824BF2237}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1211,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM500"/>
+  <dimension ref="A1:AN500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -1235,12 +1235,12 @@
     <col min="23" max="26" width="7" customWidth="1"/>
     <col min="27" max="28" width="5" customWidth="1"/>
     <col min="29" max="36" width="7" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" customWidth="1"/>
+    <col min="37" max="37" width="3.42578125" customWidth="1"/>
     <col min="38" max="39" width="7" customWidth="1"/>
     <col min="40" max="40" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1327,7 +1327,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1529,7 +1529,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1653,8 +1653,12 @@
         <f>SUM(AM6:AM500)</f>
         <v>3200</v>
       </c>
-    </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN5" s="4">
+        <f>SUM(AN6:AN500)</f>
+        <v>8995.9327999999987</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -1763,8 +1767,12 @@
         <f>ROUND(G6*Z6,0)</f>
         <v>250</v>
       </c>
-    </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN6">
+        <f>W6*G6</f>
+        <v>373.97739999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -1866,15 +1874,19 @@
       </c>
       <c r="AK7" s="1"/>
       <c r="AL7" s="1">
-        <f t="shared" ref="AL7:AM70" si="10">ROUND(G7*Y7,0)</f>
+        <f t="shared" ref="AL7:AL70" si="10">ROUND(G7*Y7,0)</f>
         <v>530</v>
       </c>
       <c r="AM7" s="1">
         <f t="shared" ref="AM7:AM70" si="11">ROUND(G7*Z7,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN7">
+        <f t="shared" ref="AN7:AN70" si="12">W7*G7</f>
+        <v>195.1114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -1986,8 +1998,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN8">
+        <f t="shared" si="12"/>
+        <v>615.27340000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
@@ -2094,8 +2110,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN9">
+        <f t="shared" si="12"/>
+        <v>1.1199999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>45</v>
       </c>
@@ -2205,8 +2225,12 @@
         <f t="shared" si="11"/>
         <v>225</v>
       </c>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN10">
+        <f t="shared" si="12"/>
+        <v>202.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>48</v>
       </c>
@@ -2321,8 +2345,12 @@
         <f t="shared" si="11"/>
         <v>225</v>
       </c>
-    </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN11">
+        <f t="shared" si="12"/>
+        <v>292.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>50</v>
       </c>
@@ -2427,8 +2455,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN12">
+        <f t="shared" si="12"/>
+        <v>3.2300000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>51</v>
       </c>
@@ -2533,8 +2565,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN13">
+        <f t="shared" si="12"/>
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -2640,8 +2676,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN14">
+        <f t="shared" si="12"/>
+        <v>3.3320000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>54</v>
       </c>
@@ -2743,8 +2783,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN15">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,8 +2898,12 @@
         <f t="shared" si="11"/>
         <v>400</v>
       </c>
-    </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN16">
+        <f t="shared" si="12"/>
+        <v>558.35879999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>58</v>
       </c>
@@ -2965,8 +3013,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN17">
+        <f t="shared" si="12"/>
+        <v>436.02780000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>59</v>
       </c>
@@ -3068,8 +3120,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN18">
+        <f t="shared" si="12"/>
+        <v>0.70620000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>60</v>
       </c>
@@ -3169,8 +3225,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN19">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>62</v>
       </c>
@@ -3262,8 +3322,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN20">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>64</v>
       </c>
@@ -3367,8 +3431,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN21">
+        <f t="shared" si="12"/>
+        <v>0.4748</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>66</v>
       </c>
@@ -3472,8 +3540,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN22">
+        <f t="shared" si="12"/>
+        <v>757.01940000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>67</v>
       </c>
@@ -3569,8 +3641,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN23">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>69</v>
       </c>
@@ -3675,8 +3751,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN24">
+        <f t="shared" si="12"/>
+        <v>134.7364</v>
+      </c>
+    </row>
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>70</v>
       </c>
@@ -3782,8 +3862,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN25">
+        <f t="shared" si="12"/>
+        <v>205.86320000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>71</v>
       </c>
@@ -3875,8 +3959,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN26">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -3985,8 +4073,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN27">
+        <f t="shared" si="12"/>
+        <v>357.56239999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>73</v>
       </c>
@@ -4090,8 +4182,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN28">
+        <f t="shared" si="12"/>
+        <v>2.1844000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>75</v>
       </c>
@@ -4185,8 +4281,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN29">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>76</v>
       </c>
@@ -4278,8 +4378,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN30">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>77</v>
       </c>
@@ -4371,8 +4475,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN31">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>78</v>
       </c>
@@ -4482,8 +4590,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN32">
+        <f t="shared" si="12"/>
+        <v>248.68560000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>79</v>
       </c>
@@ -4581,8 +4693,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN33">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
@@ -4694,8 +4810,12 @@
         <f t="shared" si="11"/>
         <v>500</v>
       </c>
-    </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN34">
+        <f t="shared" si="12"/>
+        <v>91.550399999999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>81</v>
       </c>
@@ -4787,8 +4907,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>82</v>
       </c>
@@ -4880,8 +5004,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN36">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>83</v>
       </c>
@@ -4973,8 +5101,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN37">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>84</v>
       </c>
@@ -4995,11 +5127,11 @@
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
       <c r="L38" s="9">
-        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>0</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" ref="M38:M69" si="13">E38-N38</f>
+        <f t="shared" ref="M38:M69" si="14">E38-N38</f>
         <v>0</v>
       </c>
       <c r="N38" s="9"/>
@@ -5014,7 +5146,7 @@
       <c r="U38" s="9"/>
       <c r="V38" s="9"/>
       <c r="W38" s="9">
-        <f t="shared" ref="W38:W69" si="14">M38/5</f>
+        <f t="shared" ref="W38:W69" si="15">M38/5</f>
         <v>0</v>
       </c>
       <c r="X38" s="11"/>
@@ -5066,8 +5198,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN38">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>85</v>
       </c>
@@ -5100,11 +5236,11 @@
         <v>3386</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-671</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2013</v>
       </c>
       <c r="N39" s="1">
@@ -5125,7 +5261,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>402.6</v>
       </c>
       <c r="X39" s="5">
@@ -5179,8 +5315,12 @@
         <f t="shared" si="11"/>
         <v>200</v>
       </c>
-    </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN39">
+        <f t="shared" si="12"/>
+        <v>161.04000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>86</v>
       </c>
@@ -5213,11 +5353,11 @@
         <v>771</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-258</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>513</v>
       </c>
       <c r="N40" s="1"/>
@@ -5234,7 +5374,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>102.6</v>
       </c>
       <c r="X40" s="5"/>
@@ -5286,8 +5426,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN40">
+        <f t="shared" si="12"/>
+        <v>46.17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>88</v>
       </c>
@@ -5320,11 +5464,11 @@
         <v>1679</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1452</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>227</v>
       </c>
       <c r="N41" s="1"/>
@@ -5345,7 +5489,7 @@
       </c>
       <c r="V41" s="1"/>
       <c r="W41" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45.4</v>
       </c>
       <c r="X41" s="5">
@@ -5399,8 +5543,12 @@
         <f t="shared" si="11"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN41">
+        <f t="shared" si="12"/>
+        <v>18.16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>90</v>
       </c>
@@ -5431,11 +5579,11 @@
         <v>624</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-626</v>
       </c>
       <c r="M42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-2</v>
       </c>
       <c r="N42" s="1"/>
@@ -5454,7 +5602,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.4</v>
       </c>
       <c r="X42" s="5">
@@ -5508,8 +5656,12 @@
         <f t="shared" si="11"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN42">
+        <f t="shared" si="12"/>
+        <v>-0.16000000000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>91</v>
       </c>
@@ -5538,11 +5690,11 @@
         <v>139.1</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-92.328000000000003</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>46.771999999999998</v>
       </c>
       <c r="N43" s="1"/>
@@ -5559,7 +5711,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.3544</v>
       </c>
       <c r="X43" s="5">
@@ -5616,8 +5768,12 @@
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN43">
+        <f t="shared" si="12"/>
+        <v>9.3544</v>
+      </c>
+    </row>
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>93</v>
       </c>
@@ -5650,11 +5806,11 @@
         <v>235</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-23</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>212</v>
       </c>
       <c r="N44" s="1"/>
@@ -5669,7 +5825,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42.4</v>
       </c>
       <c r="X44" s="5">
@@ -5722,8 +5878,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN44">
+        <f t="shared" si="12"/>
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>94</v>
       </c>
@@ -5752,11 +5912,11 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-6</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-6</v>
       </c>
       <c r="N45" s="1"/>
@@ -5775,7 +5935,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-1.2</v>
       </c>
       <c r="X45" s="5">
@@ -5827,8 +5987,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN45">
+        <f t="shared" si="12"/>
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>95</v>
       </c>
@@ -5861,11 +6025,11 @@
         <v>14.2</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.8509999999999991</v>
       </c>
       <c r="M46" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.349</v>
       </c>
       <c r="N46" s="1"/>
@@ -5882,7 +6046,7 @@
       </c>
       <c r="V46" s="1"/>
       <c r="W46" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.4698000000000002</v>
       </c>
       <c r="X46" s="5">
@@ -5934,8 +6098,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN46">
+        <f t="shared" si="12"/>
+        <v>2.4698000000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>97</v>
       </c>
@@ -5968,11 +6136,11 @@
         <v>200</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-76</v>
       </c>
       <c r="M47" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>124</v>
       </c>
       <c r="N47" s="1"/>
@@ -5989,7 +6157,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24.8</v>
       </c>
       <c r="X47" s="5">
@@ -6042,8 +6210,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN47">
+        <f t="shared" si="12"/>
+        <v>9.9200000000000017</v>
+      </c>
+    </row>
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>98</v>
       </c>
@@ -6076,11 +6248,11 @@
         <v>355</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-127</v>
       </c>
       <c r="M48" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>228</v>
       </c>
       <c r="N48" s="1"/>
@@ -6097,7 +6269,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45.6</v>
       </c>
       <c r="X48" s="5">
@@ -6149,8 +6321,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN48">
+        <f t="shared" si="12"/>
+        <v>18.240000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>99</v>
       </c>
@@ -6181,11 +6357,11 @@
         <v>34.9</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-34.9</v>
       </c>
       <c r="M49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N49" s="1"/>
@@ -6200,7 +6376,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X49" s="5"/>
@@ -6252,8 +6428,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>100</v>
       </c>
@@ -6286,11 +6466,11 @@
         <v>379</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-41</v>
       </c>
       <c r="M50" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>248</v>
       </c>
       <c r="N50" s="1">
@@ -6311,7 +6491,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>49.6</v>
       </c>
       <c r="X50" s="5">
@@ -6363,8 +6543,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN50">
+        <f t="shared" si="12"/>
+        <v>17.36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>101</v>
       </c>
@@ -6397,11 +6581,11 @@
         <v>524</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-103</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>421</v>
       </c>
       <c r="N51" s="1"/>
@@ -6418,7 +6602,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>84.2</v>
       </c>
       <c r="X51" s="5">
@@ -6470,8 +6654,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN51">
+        <f t="shared" si="12"/>
+        <v>33.68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
@@ -6504,11 +6692,11 @@
         <v>175.15899999999999</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-9.4639999999999986</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>67.835999999999999</v>
       </c>
       <c r="N52" s="1">
@@ -6525,7 +6713,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.5672</v>
       </c>
       <c r="X52" s="5"/>
@@ -6575,8 +6763,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN52">
+        <f t="shared" si="12"/>
+        <v>13.5672</v>
+      </c>
+    </row>
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>103</v>
       </c>
@@ -6609,11 +6801,11 @@
         <v>821.82100000000003</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-5.6979999999999791</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>816.12300000000005</v>
       </c>
       <c r="N53" s="1"/>
@@ -6630,7 +6822,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>163.22460000000001</v>
       </c>
       <c r="X53" s="5">
@@ -6683,8 +6875,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN53">
+        <f t="shared" si="12"/>
+        <v>163.22460000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>104</v>
       </c>
@@ -6705,11 +6901,11 @@
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
       <c r="L54" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M54" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N54" s="9"/>
@@ -6724,7 +6920,7 @@
       <c r="U54" s="9"/>
       <c r="V54" s="9"/>
       <c r="W54" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X54" s="11"/>
@@ -6776,8 +6972,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN54">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>105</v>
       </c>
@@ -6810,11 +7010,11 @@
         <v>329</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-51</v>
       </c>
       <c r="M55" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>218</v>
       </c>
       <c r="N55" s="1">
@@ -6833,7 +7033,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43.6</v>
       </c>
       <c r="X55" s="5"/>
@@ -6883,8 +7083,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN55">
+        <f t="shared" si="12"/>
+        <v>19.62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>106</v>
       </c>
@@ -6917,11 +7121,11 @@
         <v>530</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-43</v>
       </c>
       <c r="M56" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>487</v>
       </c>
       <c r="N56" s="1"/>
@@ -6938,7 +7142,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>97.4</v>
       </c>
       <c r="X56" s="5"/>
@@ -6988,8 +7192,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN56">
+        <f t="shared" si="12"/>
+        <v>43.830000000000005</v>
+      </c>
+    </row>
+    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>107</v>
       </c>
@@ -7010,11 +7218,11 @@
       <c r="J57" s="9"/>
       <c r="K57" s="9"/>
       <c r="L57" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M57" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N57" s="9"/>
@@ -7029,7 +7237,7 @@
       <c r="U57" s="9"/>
       <c r="V57" s="9"/>
       <c r="W57" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X57" s="11"/>
@@ -7081,8 +7289,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN57">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>108</v>
       </c>
@@ -7115,11 +7327,11 @@
         <v>49</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-16</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>33</v>
       </c>
       <c r="N58" s="1"/>
@@ -7134,7 +7346,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.6</v>
       </c>
       <c r="X58" s="5">
@@ -7187,8 +7399,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN58">
+        <f t="shared" si="12"/>
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>109</v>
       </c>
@@ -7221,11 +7437,11 @@
         <v>636.505</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-16.567000000000007</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>404.23299999999995</v>
       </c>
       <c r="N59" s="1">
@@ -7242,7 +7458,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>80.846599999999995</v>
       </c>
       <c r="X59" s="5">
@@ -7295,8 +7511,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN59">
+        <f t="shared" si="12"/>
+        <v>80.846599999999995</v>
+      </c>
+    </row>
+    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>110</v>
       </c>
@@ -7329,11 +7549,11 @@
         <v>143</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-10</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>133</v>
       </c>
       <c r="N60" s="1"/>
@@ -7348,7 +7568,7 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>26.6</v>
       </c>
       <c r="X60" s="5">
@@ -7401,8 +7621,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN60">
+        <f t="shared" si="12"/>
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>111</v>
       </c>
@@ -7435,11 +7659,11 @@
         <v>761.68299999999999</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-17.404999999999973</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>744.27800000000002</v>
       </c>
       <c r="N61" s="1"/>
@@ -7454,7 +7678,7 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>148.85560000000001</v>
       </c>
       <c r="X61" s="5">
@@ -7509,8 +7733,12 @@
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="62" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN61">
+        <f t="shared" si="12"/>
+        <v>148.85560000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>112</v>
       </c>
@@ -7543,11 +7771,11 @@
         <v>37.1</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2.9400000000000048</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>34.159999999999997</v>
       </c>
       <c r="N62" s="1"/>
@@ -7562,7 +7790,7 @@
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.831999999999999</v>
       </c>
       <c r="X62" s="5">
@@ -7615,8 +7843,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN62">
+        <f t="shared" si="12"/>
+        <v>6.831999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>113</v>
       </c>
@@ -7649,11 +7881,11 @@
         <v>97</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>93</v>
       </c>
       <c r="N63" s="1"/>
@@ -7668,7 +7900,7 @@
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18.600000000000001</v>
       </c>
       <c r="X63" s="5"/>
@@ -7718,8 +7950,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN63">
+        <f t="shared" si="12"/>
+        <v>1.8600000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>114</v>
       </c>
@@ -7748,11 +7984,11 @@
         <v>11</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-11</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N64" s="1"/>
@@ -7767,7 +8003,7 @@
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X64" s="5"/>
@@ -7819,8 +8055,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN64">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>115</v>
       </c>
@@ -7853,11 +8093,11 @@
         <v>335.9</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-57.87299999999999</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>278.02699999999999</v>
       </c>
       <c r="N65" s="1"/>
@@ -7874,7 +8114,7 @@
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>55.605399999999996</v>
       </c>
       <c r="X65" s="5">
@@ -7928,8 +8168,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN65">
+        <f t="shared" si="12"/>
+        <v>55.605399999999996</v>
+      </c>
+    </row>
+    <row r="66" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>117</v>
       </c>
@@ -7962,11 +8206,11 @@
         <v>276.10199999999998</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-112.08599999999998</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>164.01599999999999</v>
       </c>
       <c r="N66" s="1"/>
@@ -7983,7 +8227,7 @@
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
       <c r="W66" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>32.803199999999997</v>
       </c>
       <c r="X66" s="5">
@@ -8037,8 +8281,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN66">
+        <f t="shared" si="12"/>
+        <v>32.803199999999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>118</v>
       </c>
@@ -8071,11 +8319,11 @@
         <v>1283</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-281</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1002</v>
       </c>
       <c r="N67" s="1"/>
@@ -8092,7 +8340,7 @@
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>200.4</v>
       </c>
       <c r="X67" s="5">
@@ -8145,8 +8393,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN67">
+        <f t="shared" si="12"/>
+        <v>80.160000000000011</v>
+      </c>
+    </row>
+    <row r="68" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>119</v>
       </c>
@@ -8179,11 +8431,11 @@
         <v>597</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-348</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>189</v>
       </c>
       <c r="N68" s="1">
@@ -8202,7 +8454,7 @@
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
       <c r="W68" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>37.799999999999997</v>
       </c>
       <c r="X68" s="5">
@@ -8254,8 +8506,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN68">
+        <f t="shared" si="12"/>
+        <v>15.12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>120</v>
       </c>
@@ -8288,11 +8544,11 @@
         <v>88.058000000000007</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.30900000000001171</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>55.090999999999994</v>
       </c>
       <c r="N69" s="1">
@@ -8309,7 +8565,7 @@
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11.018199999999998</v>
       </c>
       <c r="X69" s="5">
@@ -8362,8 +8618,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN69">
+        <f t="shared" si="12"/>
+        <v>11.018199999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>121</v>
       </c>
@@ -8396,11 +8656,11 @@
         <v>164.452</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="15">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="16">E70-K70</f>
         <v>-2.3479999999999848</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" ref="M70:M101" si="16">E70-N70</f>
+        <f t="shared" ref="M70:M101" si="17">E70-N70</f>
         <v>162.10400000000001</v>
       </c>
       <c r="N70" s="1"/>
@@ -8415,7 +8675,7 @@
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1">
-        <f t="shared" ref="W70:W101" si="17">M70/5</f>
+        <f t="shared" ref="W70:W101" si="18">M70/5</f>
         <v>32.4208</v>
       </c>
       <c r="X70" s="5">
@@ -8468,8 +8728,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN70">
+        <f t="shared" si="12"/>
+        <v>32.4208</v>
+      </c>
+    </row>
+    <row r="71" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>122</v>
       </c>
@@ -8502,11 +8766,11 @@
         <v>587.79999999999995</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.6400000000001</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>503.74000000000007</v>
       </c>
       <c r="N71" s="1">
@@ -8523,7 +8787,7 @@
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>100.74800000000002</v>
       </c>
       <c r="X71" s="5">
@@ -8531,18 +8795,18 @@
         <v>644.33919999999989</v>
       </c>
       <c r="Y71" s="5">
-        <f t="shared" ref="Y71:Y134" si="18">X71</f>
+        <f t="shared" ref="Y71:Y134" si="19">X71</f>
         <v>644.33919999999989</v>
       </c>
       <c r="Z71" s="5">
         <v>200</v>
       </c>
       <c r="AA71" s="1">
-        <f t="shared" ref="AA71:AA134" si="19">(F71+O71+P71+Q71+R71+S71+T71+Y71+V71+U71+Z71)/W71</f>
+        <f t="shared" ref="AA71:AA134" si="20">(F71+O71+P71+Q71+R71+S71+T71+Y71+V71+U71+Z71)/W71</f>
         <v>11.985151069996425</v>
       </c>
       <c r="AB71" s="1">
-        <f t="shared" ref="AB71:AB134" si="20">(F71+O71+P71+Q71+R71+S71+T71+U71+V71)/W71</f>
+        <f t="shared" ref="AB71:AB134" si="21">(F71+O71+P71+Q71+R71+S71+T71+U71+V71)/W71</f>
         <v>3.6044467383967937</v>
       </c>
       <c r="AC71" s="1">
@@ -8571,15 +8835,19 @@
       </c>
       <c r="AK71" s="1"/>
       <c r="AL71" s="1">
-        <f t="shared" ref="AL71:AM134" si="21">ROUND(G71*Y71,0)</f>
+        <f t="shared" ref="AL71:AL134" si="22">ROUND(G71*Y71,0)</f>
         <v>644</v>
       </c>
       <c r="AM71" s="1">
-        <f t="shared" ref="AM71:AM134" si="22">ROUND(G71*Z71,0)</f>
+        <f t="shared" ref="AM71:AM134" si="23">ROUND(G71*Z71,0)</f>
         <v>200</v>
       </c>
-    </row>
-    <row r="72" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN71">
+        <f t="shared" ref="AN71:AN134" si="24">W71*G71</f>
+        <v>100.74800000000002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>123</v>
       </c>
@@ -8612,11 +8880,11 @@
         <v>114.715</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-12.754000000000005</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>101.961</v>
       </c>
       <c r="N72" s="1"/>
@@ -8631,7 +8899,7 @@
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
       <c r="W72" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>20.392199999999999</v>
       </c>
       <c r="X72" s="5">
@@ -8639,16 +8907,16 @@
         <v>120.80619999999998</v>
       </c>
       <c r="Y72" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>120.80619999999998</v>
       </c>
       <c r="Z72" s="5"/>
       <c r="AA72" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8</v>
       </c>
       <c r="AB72" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.0758623395219749</v>
       </c>
       <c r="AC72" s="1">
@@ -8677,15 +8945,19 @@
       </c>
       <c r="AK72" s="1"/>
       <c r="AL72" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>121</v>
       </c>
       <c r="AM72" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN72">
+        <f t="shared" si="24"/>
+        <v>20.392199999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
         <v>124</v>
       </c>
@@ -8706,11 +8978,11 @@
       <c r="J73" s="9"/>
       <c r="K73" s="9"/>
       <c r="L73" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M73" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N73" s="9"/>
@@ -8725,23 +8997,23 @@
       <c r="U73" s="9"/>
       <c r="V73" s="9"/>
       <c r="W73" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="X73" s="11"/>
       <c r="Y73" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z73" s="5"/>
       <c r="AA73" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB73" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB73" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC73" s="9">
         <v>0</v>
       </c>
@@ -8770,15 +9042,19 @@
         <v>63</v>
       </c>
       <c r="AL73" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM73" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN73">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>125</v>
       </c>
@@ -8811,11 +9087,11 @@
         <v>549.70000000000005</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-64.753000000000043</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>484.947</v>
       </c>
       <c r="N74" s="1"/>
@@ -8830,7 +9106,7 @@
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
       <c r="W74" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>96.989400000000003</v>
       </c>
       <c r="X74" s="5">
@@ -8838,16 +9114,16 @@
         <v>580.25020000000018</v>
       </c>
       <c r="Y74" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>580.25020000000018</v>
       </c>
       <c r="Z74" s="5"/>
       <c r="AA74" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
       <c r="AB74" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.0173854050030204</v>
       </c>
       <c r="AC74" s="1">
@@ -8876,15 +9152,19 @@
       </c>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>580</v>
       </c>
       <c r="AM74" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN74">
+        <f t="shared" si="24"/>
+        <v>96.989400000000003</v>
+      </c>
+    </row>
+    <row r="75" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
         <v>126</v>
       </c>
@@ -8909,11 +9189,11 @@
       <c r="J75" s="9"/>
       <c r="K75" s="9"/>
       <c r="L75" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M75" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N75" s="9"/>
@@ -8928,23 +9208,23 @@
       <c r="U75" s="9"/>
       <c r="V75" s="9"/>
       <c r="W75" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="X75" s="11"/>
       <c r="Y75" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z75" s="5"/>
       <c r="AA75" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB75" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB75" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC75" s="9">
         <v>0.2</v>
       </c>
@@ -8971,15 +9251,19 @@
       </c>
       <c r="AK75" s="9"/>
       <c r="AL75" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM75" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN75">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>127</v>
       </c>
@@ -9012,11 +9296,11 @@
         <v>567</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-157</v>
       </c>
       <c r="M76" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>410</v>
       </c>
       <c r="N76" s="1"/>
@@ -9033,23 +9317,23 @@
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>82</v>
       </c>
       <c r="X76" s="5"/>
       <c r="Y76" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z76" s="5"/>
       <c r="AA76" s="1">
-        <f t="shared" si="19"/>
-        <v>19.899461463414632</v>
-      </c>
-      <c r="AB76" s="1">
         <f t="shared" si="20"/>
         <v>19.899461463414632</v>
       </c>
+      <c r="AB76" s="1">
+        <f t="shared" si="21"/>
+        <v>19.899461463414632</v>
+      </c>
       <c r="AC76" s="1">
         <v>127.8</v>
       </c>
@@ -9076,15 +9360,19 @@
       </c>
       <c r="AK76" s="1"/>
       <c r="AL76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM76" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN76">
+        <f t="shared" si="24"/>
+        <v>49.199999999999996</v>
+      </c>
+    </row>
+    <row r="77" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>128</v>
       </c>
@@ -9117,11 +9405,11 @@
         <v>571</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-110</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>461</v>
       </c>
       <c r="N77" s="1"/>
@@ -9136,23 +9424,23 @@
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
       <c r="W77" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>92.2</v>
       </c>
       <c r="X77" s="5"/>
       <c r="Y77" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z77" s="5"/>
       <c r="AA77" s="1">
-        <f t="shared" si="19"/>
-        <v>17.309067245119309</v>
-      </c>
-      <c r="AB77" s="1">
         <f t="shared" si="20"/>
         <v>17.309067245119309</v>
       </c>
+      <c r="AB77" s="1">
+        <f t="shared" si="21"/>
+        <v>17.309067245119309</v>
+      </c>
       <c r="AC77" s="1">
         <v>129.19999999999999</v>
       </c>
@@ -9179,15 +9467,19 @@
       </c>
       <c r="AK77" s="1"/>
       <c r="AL77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM77" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN77">
+        <f t="shared" si="24"/>
+        <v>55.32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>129</v>
       </c>
@@ -9216,11 +9508,11 @@
         <v>7</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-2</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="N78" s="1"/>
@@ -9235,23 +9527,23 @@
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="X78" s="5"/>
       <c r="Y78" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z78" s="5"/>
       <c r="AA78" s="1">
-        <f t="shared" si="19"/>
-        <v>51</v>
-      </c>
-      <c r="AB78" s="1">
         <f t="shared" si="20"/>
         <v>51</v>
       </c>
+      <c r="AB78" s="1">
+        <f t="shared" si="21"/>
+        <v>51</v>
+      </c>
       <c r="AC78" s="1">
         <v>0</v>
       </c>
@@ -9280,15 +9572,19 @@
         <v>130</v>
       </c>
       <c r="AL78" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM78" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN78">
+        <f t="shared" si="24"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
         <v>131</v>
       </c>
@@ -9315,11 +9611,11 @@
         <v>1</v>
       </c>
       <c r="L79" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M79" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N79" s="9"/>
@@ -9334,23 +9630,23 @@
       <c r="U79" s="9"/>
       <c r="V79" s="9"/>
       <c r="W79" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="X79" s="11"/>
       <c r="Y79" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z79" s="5"/>
       <c r="AA79" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB79" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB79" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC79" s="9">
         <v>0</v>
       </c>
@@ -9379,15 +9675,19 @@
         <v>63</v>
       </c>
       <c r="AL79" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM79" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN79">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>132</v>
       </c>
@@ -9420,11 +9720,11 @@
         <v>48</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-22</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>26</v>
       </c>
       <c r="N80" s="1"/>
@@ -9439,7 +9739,7 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.2</v>
       </c>
       <c r="X80" s="5">
@@ -9447,16 +9747,16 @@
         <v>6.2000000000000028</v>
       </c>
       <c r="Y80" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.2000000000000028</v>
       </c>
       <c r="Z80" s="5"/>
       <c r="AA80" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11</v>
       </c>
       <c r="AB80" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9.8076923076923066</v>
       </c>
       <c r="AC80" s="1">
@@ -9485,15 +9785,19 @@
       </c>
       <c r="AK80" s="1"/>
       <c r="AL80" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="AM80" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN80">
+        <f t="shared" si="24"/>
+        <v>1.8199999999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>133</v>
       </c>
@@ -9526,11 +9830,11 @@
         <v>107</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>106</v>
       </c>
       <c r="N81" s="1"/>
@@ -9545,23 +9849,23 @@
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>21.2</v>
       </c>
       <c r="X81" s="5"/>
       <c r="Y81" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z81" s="5"/>
       <c r="AA81" s="1">
-        <f t="shared" si="19"/>
-        <v>15.216981132075473</v>
-      </c>
-      <c r="AB81" s="1">
         <f t="shared" si="20"/>
         <v>15.216981132075473</v>
       </c>
+      <c r="AB81" s="1">
+        <f t="shared" si="21"/>
+        <v>15.216981132075473</v>
+      </c>
       <c r="AC81" s="1">
         <v>30.6</v>
       </c>
@@ -9588,15 +9892,19 @@
       </c>
       <c r="AK81" s="1"/>
       <c r="AL81" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM81" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN81">
+        <f t="shared" si="24"/>
+        <v>7.8439999999999994</v>
+      </c>
+    </row>
+    <row r="82" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>134</v>
       </c>
@@ -9629,11 +9937,11 @@
         <v>243</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-39</v>
       </c>
       <c r="M82" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>204</v>
       </c>
       <c r="N82" s="1"/>
@@ -9648,23 +9956,23 @@
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>40.799999999999997</v>
       </c>
       <c r="X82" s="5"/>
       <c r="Y82" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z82" s="5"/>
       <c r="AA82" s="1">
-        <f t="shared" si="19"/>
-        <v>13.941176470588236</v>
-      </c>
-      <c r="AB82" s="1">
         <f t="shared" si="20"/>
         <v>13.941176470588236</v>
       </c>
+      <c r="AB82" s="1">
+        <f t="shared" si="21"/>
+        <v>13.941176470588236</v>
+      </c>
       <c r="AC82" s="1">
         <v>61.8</v>
       </c>
@@ -9693,15 +10001,19 @@
         <v>135</v>
       </c>
       <c r="AL82" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM82" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN82">
+        <f t="shared" si="24"/>
+        <v>24.479999999999997</v>
+      </c>
+    </row>
+    <row r="83" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>136</v>
       </c>
@@ -9734,11 +10046,11 @@
         <v>325</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-71</v>
       </c>
       <c r="M83" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>254</v>
       </c>
       <c r="N83" s="1"/>
@@ -9753,7 +10065,7 @@
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>50.8</v>
       </c>
       <c r="X83" s="5">
@@ -9761,16 +10073,16 @@
         <v>59.011200000000031</v>
       </c>
       <c r="Y83" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>59.011200000000031</v>
       </c>
       <c r="Z83" s="5"/>
       <c r="AA83" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11</v>
       </c>
       <c r="AB83" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9.8383622047244081</v>
       </c>
       <c r="AC83" s="1">
@@ -9799,15 +10111,19 @@
       </c>
       <c r="AK83" s="1"/>
       <c r="AL83" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>19</v>
       </c>
       <c r="AM83" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN83">
+        <f t="shared" si="24"/>
+        <v>16.763999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>137</v>
       </c>
@@ -9840,11 +10156,11 @@
         <v>42</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-13</v>
       </c>
       <c r="M84" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>29</v>
       </c>
       <c r="N84" s="1"/>
@@ -9859,23 +10175,23 @@
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.8</v>
       </c>
       <c r="X84" s="5"/>
       <c r="Y84" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z84" s="5"/>
       <c r="AA84" s="1">
-        <f t="shared" si="19"/>
-        <v>25.724137931034488</v>
-      </c>
-      <c r="AB84" s="1">
         <f t="shared" si="20"/>
         <v>25.724137931034488</v>
       </c>
+      <c r="AB84" s="1">
+        <f t="shared" si="21"/>
+        <v>25.724137931034488</v>
+      </c>
       <c r="AC84" s="1">
         <v>13.2</v>
       </c>
@@ -9902,15 +10218,19 @@
       </c>
       <c r="AK84" s="1"/>
       <c r="AL84" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM84" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN84">
+        <f t="shared" si="24"/>
+        <v>2.3199999999999998</v>
+      </c>
+    </row>
+    <row r="85" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>138</v>
       </c>
@@ -9943,11 +10263,11 @@
         <v>272</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-11</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>261</v>
       </c>
       <c r="N85" s="1"/>
@@ -9966,25 +10286,25 @@
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>52.2</v>
       </c>
       <c r="X85" s="5">
         <v>150</v>
       </c>
       <c r="Y85" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>150</v>
       </c>
       <c r="Z85" s="5">
         <v>100</v>
       </c>
       <c r="AA85" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.6398467432950188</v>
       </c>
       <c r="AB85" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.8505747126436778</v>
       </c>
       <c r="AC85" s="1">
@@ -10013,15 +10333,19 @@
       </c>
       <c r="AK85" s="1"/>
       <c r="AL85" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>53</v>
       </c>
       <c r="AM85" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="86" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN85">
+        <f t="shared" si="24"/>
+        <v>18.27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>139</v>
       </c>
@@ -10054,11 +10378,11 @@
         <v>519</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-164</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>205</v>
       </c>
       <c r="N86" s="1">
@@ -10077,7 +10401,7 @@
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>41</v>
       </c>
       <c r="X86" s="5">
@@ -10085,18 +10409,18 @@
         <v>197</v>
       </c>
       <c r="Y86" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>197</v>
       </c>
       <c r="Z86" s="5">
         <v>100</v>
       </c>
       <c r="AA86" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13.439024390243903</v>
       </c>
       <c r="AB86" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.1951219512195124</v>
       </c>
       <c r="AC86" s="1">
@@ -10125,15 +10449,19 @@
       </c>
       <c r="AK86" s="1"/>
       <c r="AL86" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>69</v>
       </c>
       <c r="AM86" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="87" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN86">
+        <f t="shared" si="24"/>
+        <v>14.35</v>
+      </c>
+    </row>
+    <row r="87" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
         <v>140</v>
       </c>
@@ -10160,11 +10488,11 @@
       </c>
       <c r="K87" s="9"/>
       <c r="L87" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M87" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N87" s="9"/>
@@ -10179,23 +10507,23 @@
       <c r="U87" s="9"/>
       <c r="V87" s="9"/>
       <c r="W87" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="X87" s="11"/>
       <c r="Y87" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z87" s="5"/>
       <c r="AA87" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB87" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB87" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC87" s="9">
         <v>0</v>
       </c>
@@ -10222,15 +10550,19 @@
       </c>
       <c r="AK87" s="9"/>
       <c r="AL87" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM87" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN87">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>141</v>
       </c>
@@ -10259,11 +10591,11 @@
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N88" s="1"/>
@@ -10278,23 +10610,23 @@
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="X88" s="5"/>
       <c r="Y88" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z88" s="5"/>
       <c r="AA88" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB88" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB88" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC88" s="1">
         <v>0.4</v>
       </c>
@@ -10323,15 +10655,19 @@
         <v>74</v>
       </c>
       <c r="AL88" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM88" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN88">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>142</v>
       </c>
@@ -10364,11 +10700,11 @@
         <v>12.2</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-9.3019999999999996</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.8980000000000001</v>
       </c>
       <c r="N89" s="1"/>
@@ -10383,23 +10719,23 @@
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.5796</v>
       </c>
       <c r="X89" s="5"/>
       <c r="Y89" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z89" s="5"/>
       <c r="AA89" s="1">
-        <f t="shared" si="19"/>
-        <v>48.464458247066943</v>
-      </c>
-      <c r="AB89" s="1">
         <f t="shared" si="20"/>
         <v>48.464458247066943</v>
       </c>
+      <c r="AB89" s="1">
+        <f t="shared" si="21"/>
+        <v>48.464458247066943</v>
+      </c>
       <c r="AC89" s="1">
         <v>0.81820000000000004</v>
       </c>
@@ -10428,15 +10764,19 @@
         <v>74</v>
       </c>
       <c r="AL89" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM89" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN89">
+        <f t="shared" si="24"/>
+        <v>0.5796</v>
+      </c>
+    </row>
+    <row r="90" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
         <v>143</v>
       </c>
@@ -10457,11 +10797,11 @@
       <c r="J90" s="9"/>
       <c r="K90" s="9"/>
       <c r="L90" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M90" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N90" s="9"/>
@@ -10476,23 +10816,23 @@
       <c r="U90" s="9"/>
       <c r="V90" s="9"/>
       <c r="W90" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="X90" s="11"/>
       <c r="Y90" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z90" s="5"/>
       <c r="AA90" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB90" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB90" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC90" s="9">
         <v>0</v>
       </c>
@@ -10521,15 +10861,19 @@
         <v>63</v>
       </c>
       <c r="AL90" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM90" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN90">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>144</v>
       </c>
@@ -10562,11 +10906,11 @@
         <v>2812.645</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-74.005999999999858</v>
       </c>
       <c r="M91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2738.6390000000001</v>
       </c>
       <c r="N91" s="1"/>
@@ -10583,23 +10927,23 @@
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
       <c r="W91" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>547.7278</v>
       </c>
       <c r="X91" s="5"/>
       <c r="Y91" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z91" s="5"/>
       <c r="AA91" s="1">
-        <f t="shared" si="19"/>
-        <v>16.398119575326067</v>
-      </c>
-      <c r="AB91" s="1">
         <f t="shared" si="20"/>
         <v>16.398119575326067</v>
       </c>
+      <c r="AB91" s="1">
+        <f t="shared" si="21"/>
+        <v>16.398119575326067</v>
+      </c>
       <c r="AC91" s="1">
         <v>842.63180000000011</v>
       </c>
@@ -10626,15 +10970,19 @@
       </c>
       <c r="AK91" s="1"/>
       <c r="AL91" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM91" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN91">
+        <f t="shared" si="24"/>
+        <v>547.7278</v>
+      </c>
+    </row>
+    <row r="92" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>145</v>
       </c>
@@ -10667,11 +11015,11 @@
         <v>275</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-96</v>
       </c>
       <c r="M92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>179</v>
       </c>
       <c r="N92" s="1"/>
@@ -10688,23 +11036,23 @@
       </c>
       <c r="V92" s="1"/>
       <c r="W92" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>35.799999999999997</v>
       </c>
       <c r="X92" s="5">
         <v>100</v>
       </c>
       <c r="Y92" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>100</v>
       </c>
       <c r="Z92" s="5"/>
       <c r="AA92" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13.532045437616388</v>
       </c>
       <c r="AB92" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.738749348230913</v>
       </c>
       <c r="AC92" s="1">
@@ -10733,15 +11081,19 @@
       </c>
       <c r="AK92" s="1"/>
       <c r="AL92" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
       <c r="AM92" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN92">
+        <f t="shared" si="24"/>
+        <v>10.739999999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>147</v>
       </c>
@@ -10774,11 +11126,11 @@
         <v>1957.712</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-60.436999999999898</v>
       </c>
       <c r="M93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1897.2750000000001</v>
       </c>
       <c r="N93" s="1"/>
@@ -10795,23 +11147,23 @@
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>379.45500000000004</v>
       </c>
       <c r="X93" s="5"/>
       <c r="Y93" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z93" s="5"/>
       <c r="AA93" s="1">
-        <f t="shared" si="19"/>
-        <v>13.304321269212462</v>
-      </c>
-      <c r="AB93" s="1">
         <f t="shared" si="20"/>
         <v>13.304321269212462</v>
       </c>
+      <c r="AB93" s="1">
+        <f t="shared" si="21"/>
+        <v>13.304321269212462</v>
+      </c>
       <c r="AC93" s="1">
         <v>357.23480000000001</v>
       </c>
@@ -10838,15 +11190,19 @@
       </c>
       <c r="AK93" s="1"/>
       <c r="AL93" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM93" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN93">
+        <f t="shared" si="24"/>
+        <v>379.45500000000004</v>
+      </c>
+    </row>
+    <row r="94" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>148</v>
       </c>
@@ -10879,11 +11235,11 @@
         <v>3549.8870000000002</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-77.135000000000218</v>
       </c>
       <c r="M94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3472.752</v>
       </c>
       <c r="N94" s="1"/>
@@ -10902,7 +11258,7 @@
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>694.55039999999997</v>
       </c>
       <c r="X94" s="5">
@@ -10910,18 +11266,18 @@
         <v>2376.0354985295908</v>
       </c>
       <c r="Y94" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2376.0354985295908</v>
       </c>
       <c r="Z94" s="5">
         <v>500</v>
       </c>
       <c r="AA94" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.719890162038638</v>
       </c>
       <c r="AB94" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.5790308399079596</v>
       </c>
       <c r="AC94" s="1">
@@ -10950,15 +11306,19 @@
       </c>
       <c r="AK94" s="1"/>
       <c r="AL94" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2376</v>
       </c>
       <c r="AM94" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>500</v>
       </c>
-    </row>
-    <row r="95" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN94">
+        <f t="shared" si="24"/>
+        <v>694.55039999999997</v>
+      </c>
+    </row>
+    <row r="95" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>68</v>
       </c>
@@ -10992,11 +11352,11 @@
         <v>4651.7070000000003</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-133.21100000000024</v>
       </c>
       <c r="M95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4518.4960000000001</v>
       </c>
       <c r="N95" s="1"/>
@@ -11015,7 +11375,7 @@
         <v>400</v>
       </c>
       <c r="W95" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>903.69920000000002</v>
       </c>
       <c r="X95" s="5">
@@ -11023,18 +11383,18 @@
         <v>1405.7007999999996</v>
       </c>
       <c r="Y95" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1405.7007999999996</v>
       </c>
       <c r="Z95" s="5">
         <v>400</v>
       </c>
       <c r="AA95" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.4426251566893047</v>
       </c>
       <c r="AB95" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7.4445036578542956</v>
       </c>
       <c r="AC95" s="1">
@@ -11063,15 +11423,19 @@
       </c>
       <c r="AK95" s="1"/>
       <c r="AL95" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1406</v>
       </c>
       <c r="AM95" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>400</v>
       </c>
-    </row>
-    <row r="96" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN95">
+        <f t="shared" si="24"/>
+        <v>903.69920000000002</v>
+      </c>
+    </row>
+    <row r="96" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>149</v>
       </c>
@@ -11104,11 +11468,11 @@
         <v>27.52</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-7.166999999999998</v>
       </c>
       <c r="M96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>20.353000000000002</v>
       </c>
       <c r="N96" s="1"/>
@@ -11123,23 +11487,23 @@
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4.0706000000000007</v>
       </c>
       <c r="X96" s="5"/>
       <c r="Y96" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z96" s="5"/>
       <c r="AA96" s="1">
-        <f t="shared" si="19"/>
-        <v>13.510932049329336</v>
-      </c>
-      <c r="AB96" s="1">
         <f t="shared" si="20"/>
         <v>13.510932049329336</v>
       </c>
+      <c r="AB96" s="1">
+        <f t="shared" si="21"/>
+        <v>13.510932049329336</v>
+      </c>
       <c r="AC96" s="1">
         <v>5.3708</v>
       </c>
@@ -11166,15 +11530,19 @@
       </c>
       <c r="AK96" s="1"/>
       <c r="AL96" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM96" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN96">
+        <f t="shared" si="24"/>
+        <v>4.0706000000000007</v>
+      </c>
+    </row>
+    <row r="97" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
         <v>150</v>
       </c>
@@ -11199,11 +11567,11 @@
       <c r="J97" s="9"/>
       <c r="K97" s="9"/>
       <c r="L97" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M97" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N97" s="9"/>
@@ -11218,23 +11586,23 @@
       <c r="U97" s="9"/>
       <c r="V97" s="9"/>
       <c r="W97" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="X97" s="11"/>
       <c r="Y97" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z97" s="5"/>
       <c r="AA97" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB97" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB97" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC97" s="9">
         <v>0</v>
       </c>
@@ -11261,15 +11629,19 @@
       </c>
       <c r="AK97" s="9"/>
       <c r="AL97" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM97" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN97">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A98" s="9" t="s">
         <v>151</v>
       </c>
@@ -11296,11 +11668,11 @@
       <c r="J98" s="9"/>
       <c r="K98" s="9"/>
       <c r="L98" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1.016</v>
       </c>
       <c r="M98" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1.016</v>
       </c>
       <c r="N98" s="9"/>
@@ -11315,23 +11687,23 @@
       <c r="U98" s="9"/>
       <c r="V98" s="9"/>
       <c r="W98" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-0.20319999999999999</v>
       </c>
       <c r="X98" s="11"/>
       <c r="Y98" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z98" s="5"/>
       <c r="AA98" s="1">
-        <f t="shared" si="19"/>
-        <v>12.775590551181104</v>
-      </c>
-      <c r="AB98" s="1">
         <f t="shared" si="20"/>
         <v>12.775590551181104</v>
       </c>
+      <c r="AB98" s="1">
+        <f t="shared" si="21"/>
+        <v>12.775590551181104</v>
+      </c>
       <c r="AC98" s="9">
         <v>0</v>
       </c>
@@ -11358,15 +11730,19 @@
       </c>
       <c r="AK98" s="9"/>
       <c r="AL98" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM98" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN98">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>152</v>
       </c>
@@ -11397,11 +11773,11 @@
         <v>103</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-107</v>
       </c>
       <c r="M99" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4</v>
       </c>
       <c r="N99" s="1"/>
@@ -11420,23 +11796,23 @@
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-0.8</v>
       </c>
       <c r="X99" s="5">
         <v>50</v>
       </c>
       <c r="Y99" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>50</v>
       </c>
       <c r="Z99" s="5"/>
       <c r="AA99" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-115</v>
       </c>
       <c r="AB99" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-52.5</v>
       </c>
       <c r="AC99" s="1">
@@ -11465,15 +11841,19 @@
       </c>
       <c r="AK99" s="1"/>
       <c r="AL99" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="AM99" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN99">
+        <f t="shared" si="24"/>
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>153</v>
       </c>
@@ -11506,11 +11886,11 @@
         <v>46</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-5</v>
       </c>
       <c r="M100" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>41</v>
       </c>
       <c r="N100" s="1"/>
@@ -11525,23 +11905,23 @@
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="X100" s="5"/>
       <c r="Y100" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z100" s="5"/>
       <c r="AA100" s="1">
-        <f t="shared" si="19"/>
-        <v>17.073170731707318</v>
-      </c>
-      <c r="AB100" s="1">
         <f t="shared" si="20"/>
         <v>17.073170731707318</v>
       </c>
+      <c r="AB100" s="1">
+        <f t="shared" si="21"/>
+        <v>17.073170731707318</v>
+      </c>
       <c r="AC100" s="1">
         <v>7.8</v>
       </c>
@@ -11570,15 +11950,19 @@
         <v>65</v>
       </c>
       <c r="AL100" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM100" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN100">
+        <f t="shared" si="24"/>
+        <v>2.4599999999999995</v>
+      </c>
+    </row>
+    <row r="101" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>154</v>
       </c>
@@ -11611,11 +11995,11 @@
         <v>249</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-13</v>
       </c>
       <c r="M101" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>236</v>
       </c>
       <c r="N101" s="1"/>
@@ -11630,23 +12014,23 @@
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>47.2</v>
       </c>
       <c r="X101" s="5"/>
       <c r="Y101" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z101" s="5"/>
       <c r="AA101" s="1">
-        <f t="shared" si="19"/>
-        <v>12.754237288135592</v>
-      </c>
-      <c r="AB101" s="1">
         <f t="shared" si="20"/>
         <v>12.754237288135592</v>
       </c>
+      <c r="AB101" s="1">
+        <f t="shared" si="21"/>
+        <v>12.754237288135592</v>
+      </c>
       <c r="AC101" s="1">
         <v>25.4</v>
       </c>
@@ -11675,15 +12059,19 @@
         <v>155</v>
       </c>
       <c r="AL101" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM101" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN101">
+        <f t="shared" si="24"/>
+        <v>3.3040000000000007</v>
+      </c>
+    </row>
+    <row r="102" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>156</v>
       </c>
@@ -11716,11 +12104,11 @@
         <v>274</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L133" si="23">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="25">E102-K102</f>
         <v>-34</v>
       </c>
       <c r="M102" s="1">
-        <f t="shared" ref="M102:M133" si="24">E102-N102</f>
+        <f t="shared" ref="M102:M133" si="26">E102-N102</f>
         <v>240</v>
       </c>
       <c r="N102" s="1"/>
@@ -11735,23 +12123,23 @@
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1">
-        <f t="shared" ref="W102:W138" si="25">M102/5</f>
+        <f t="shared" ref="W102:W138" si="27">M102/5</f>
         <v>48</v>
       </c>
       <c r="X102" s="5"/>
       <c r="Y102" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z102" s="5"/>
       <c r="AA102" s="1">
-        <f t="shared" si="19"/>
-        <v>14.441666666666668</v>
-      </c>
-      <c r="AB102" s="1">
         <f t="shared" si="20"/>
         <v>14.441666666666668</v>
       </c>
+      <c r="AB102" s="1">
+        <f t="shared" si="21"/>
+        <v>14.441666666666668</v>
+      </c>
       <c r="AC102" s="1">
         <v>27.6</v>
       </c>
@@ -11780,15 +12168,19 @@
         <v>157</v>
       </c>
       <c r="AL102" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM102" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN102">
+        <f t="shared" si="24"/>
+        <v>3.3600000000000003</v>
+      </c>
+    </row>
+    <row r="103" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>158</v>
       </c>
@@ -11821,11 +12213,11 @@
         <v>217</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-13</v>
       </c>
       <c r="M103" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>204</v>
       </c>
       <c r="N103" s="1"/>
@@ -11840,23 +12232,23 @@
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>40.799999999999997</v>
       </c>
       <c r="X103" s="5"/>
       <c r="Y103" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z103" s="5"/>
       <c r="AA103" s="1">
-        <f t="shared" si="19"/>
-        <v>14.48529411764706</v>
-      </c>
-      <c r="AB103" s="1">
         <f t="shared" si="20"/>
         <v>14.48529411764706</v>
       </c>
+      <c r="AB103" s="1">
+        <f t="shared" si="21"/>
+        <v>14.48529411764706</v>
+      </c>
       <c r="AC103" s="1">
         <v>18.600000000000001</v>
       </c>
@@ -11885,15 +12277,19 @@
         <v>155</v>
       </c>
       <c r="AL103" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM103" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN103">
+        <f t="shared" si="24"/>
+        <v>2.8559999999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
         <v>159</v>
       </c>
@@ -11924,11 +12320,11 @@
         <v>131</v>
       </c>
       <c r="L104" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-131</v>
       </c>
       <c r="M104" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N104" s="9"/>
@@ -11943,23 +12339,23 @@
       <c r="U104" s="9"/>
       <c r="V104" s="9"/>
       <c r="W104" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X104" s="11"/>
       <c r="Y104" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z104" s="5"/>
       <c r="AA104" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB104" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB104" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC104" s="9">
         <v>-0.6</v>
       </c>
@@ -11986,15 +12382,19 @@
       </c>
       <c r="AK104" s="9"/>
       <c r="AL104" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM104" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN104">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>160</v>
       </c>
@@ -12027,11 +12427,11 @@
         <v>46</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-29</v>
       </c>
       <c r="M105" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>17</v>
       </c>
       <c r="N105" s="1"/>
@@ -12046,23 +12446,23 @@
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>3.4</v>
       </c>
       <c r="X105" s="5">
         <v>6</v>
       </c>
       <c r="Y105" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="Z105" s="5"/>
       <c r="AA105" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.941176470588234</v>
       </c>
       <c r="AB105" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.176470588235293</v>
       </c>
       <c r="AC105" s="1">
@@ -12091,15 +12491,19 @@
       </c>
       <c r="AK105" s="1"/>
       <c r="AL105" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="AM105" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN105">
+        <f t="shared" si="24"/>
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="106" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>161</v>
       </c>
@@ -12130,11 +12534,11 @@
         <v>7.2</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1.6689999999999996</v>
       </c>
       <c r="M106" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>8.8689999999999998</v>
       </c>
       <c r="N106" s="1"/>
@@ -12149,23 +12553,23 @@
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.7738</v>
       </c>
       <c r="X106" s="5"/>
       <c r="Y106" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z106" s="5"/>
       <c r="AA106" s="1">
-        <f t="shared" si="19"/>
-        <v>16.393956477618669</v>
-      </c>
-      <c r="AB106" s="1">
         <f t="shared" si="20"/>
         <v>16.393956477618669</v>
       </c>
+      <c r="AB106" s="1">
+        <f t="shared" si="21"/>
+        <v>16.393956477618669</v>
+      </c>
       <c r="AC106" s="1">
         <v>2.5558000000000001</v>
       </c>
@@ -12192,15 +12596,19 @@
       </c>
       <c r="AK106" s="1"/>
       <c r="AL106" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM106" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN106">
+        <f t="shared" si="24"/>
+        <v>1.7738</v>
+      </c>
+    </row>
+    <row r="107" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>162</v>
       </c>
@@ -12233,11 +12641,11 @@
         <v>187</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-85</v>
       </c>
       <c r="M107" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>102</v>
       </c>
       <c r="N107" s="1"/>
@@ -12252,23 +12660,23 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>20.399999999999999</v>
       </c>
       <c r="X107" s="5"/>
       <c r="Y107" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z107" s="5"/>
       <c r="AA107" s="1">
-        <f t="shared" si="19"/>
-        <v>34.686274509803923</v>
-      </c>
-      <c r="AB107" s="1">
         <f t="shared" si="20"/>
         <v>34.686274509803923</v>
       </c>
+      <c r="AB107" s="1">
+        <f t="shared" si="21"/>
+        <v>34.686274509803923</v>
+      </c>
       <c r="AC107" s="1">
         <v>18.600000000000001</v>
       </c>
@@ -12297,15 +12705,19 @@
         <v>157</v>
       </c>
       <c r="AL107" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM107" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN107">
+        <f t="shared" si="24"/>
+        <v>2.2439999999999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
         <v>163</v>
       </c>
@@ -12326,11 +12738,11 @@
       <c r="J108" s="9"/>
       <c r="K108" s="9"/>
       <c r="L108" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M108" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N108" s="9"/>
@@ -12345,23 +12757,23 @@
       <c r="U108" s="9"/>
       <c r="V108" s="9"/>
       <c r="W108" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X108" s="11"/>
       <c r="Y108" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z108" s="5"/>
       <c r="AA108" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB108" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB108" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC108" s="9">
         <v>0</v>
       </c>
@@ -12390,15 +12802,19 @@
         <v>63</v>
       </c>
       <c r="AL108" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM108" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN108">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>164</v>
       </c>
@@ -12431,11 +12847,11 @@
         <v>344</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-84</v>
       </c>
       <c r="M109" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>260</v>
       </c>
       <c r="N109" s="1"/>
@@ -12450,23 +12866,23 @@
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>52</v>
       </c>
       <c r="X109" s="5"/>
       <c r="Y109" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z109" s="5"/>
       <c r="AA109" s="1">
-        <f t="shared" si="19"/>
-        <v>14.73076923076923</v>
-      </c>
-      <c r="AB109" s="1">
         <f t="shared" si="20"/>
         <v>14.73076923076923</v>
       </c>
+      <c r="AB109" s="1">
+        <f t="shared" si="21"/>
+        <v>14.73076923076923</v>
+      </c>
       <c r="AC109" s="1">
         <v>41</v>
       </c>
@@ -12495,15 +12911,19 @@
         <v>165</v>
       </c>
       <c r="AL109" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM109" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN109">
+        <f t="shared" si="24"/>
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>166</v>
       </c>
@@ -12536,11 +12956,11 @@
         <v>329</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-106</v>
       </c>
       <c r="M110" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>223</v>
       </c>
       <c r="N110" s="1"/>
@@ -12555,23 +12975,23 @@
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>44.6</v>
       </c>
       <c r="X110" s="5"/>
       <c r="Y110" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z110" s="5"/>
       <c r="AA110" s="1">
-        <f t="shared" si="19"/>
-        <v>23.197309417040355</v>
-      </c>
-      <c r="AB110" s="1">
         <f t="shared" si="20"/>
         <v>23.197309417040355</v>
       </c>
+      <c r="AB110" s="1">
+        <f t="shared" si="21"/>
+        <v>23.197309417040355</v>
+      </c>
       <c r="AC110" s="1">
         <v>41.6</v>
       </c>
@@ -12600,15 +13020,19 @@
         <v>167</v>
       </c>
       <c r="AL110" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM110" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN110">
+        <f t="shared" si="24"/>
+        <v>3.5680000000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>168</v>
       </c>
@@ -12641,11 +13065,11 @@
         <v>162</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-33</v>
       </c>
       <c r="M111" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>129</v>
       </c>
       <c r="N111" s="1"/>
@@ -12660,23 +13084,23 @@
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>25.8</v>
       </c>
       <c r="X111" s="5"/>
       <c r="Y111" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z111" s="5"/>
       <c r="AA111" s="1">
-        <f t="shared" si="19"/>
-        <v>24.511627906976742</v>
-      </c>
-      <c r="AB111" s="1">
         <f t="shared" si="20"/>
         <v>24.511627906976742</v>
       </c>
+      <c r="AB111" s="1">
+        <f t="shared" si="21"/>
+        <v>24.511627906976742</v>
+      </c>
       <c r="AC111" s="1">
         <v>16.2</v>
       </c>
@@ -12705,15 +13129,19 @@
         <v>157</v>
       </c>
       <c r="AL111" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM111" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN111">
+        <f t="shared" si="24"/>
+        <v>4.3860000000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>169</v>
       </c>
@@ -12746,11 +13174,11 @@
         <v>205.63399999999999</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-31.501999999999981</v>
       </c>
       <c r="M112" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>174.13200000000001</v>
       </c>
       <c r="N112" s="1"/>
@@ -12771,23 +13199,23 @@
       </c>
       <c r="V112" s="1"/>
       <c r="W112" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>34.8264</v>
       </c>
       <c r="X112" s="5">
         <v>120</v>
       </c>
       <c r="Y112" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>120</v>
       </c>
       <c r="Z112" s="5"/>
       <c r="AA112" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.1020134151103749</v>
       </c>
       <c r="AB112" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.65635150345714677</v>
       </c>
       <c r="AC112" s="1">
@@ -12816,15 +13244,19 @@
       </c>
       <c r="AK112" s="1"/>
       <c r="AL112" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>120</v>
       </c>
       <c r="AM112" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN112">
+        <f t="shared" si="24"/>
+        <v>34.8264</v>
+      </c>
+    </row>
+    <row r="113" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>171</v>
       </c>
@@ -12857,11 +13289,11 @@
         <v>101.41500000000001</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-20.237000000000009</v>
       </c>
       <c r="M113" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>81.177999999999997</v>
       </c>
       <c r="N113" s="1"/>
@@ -12878,23 +13310,23 @@
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>16.235599999999998</v>
       </c>
       <c r="X113" s="5"/>
       <c r="Y113" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z113" s="5"/>
       <c r="AA113" s="1">
-        <f t="shared" si="19"/>
-        <v>11.59646086378083</v>
-      </c>
-      <c r="AB113" s="1">
         <f t="shared" si="20"/>
         <v>11.59646086378083</v>
       </c>
+      <c r="AB113" s="1">
+        <f t="shared" si="21"/>
+        <v>11.59646086378083</v>
+      </c>
       <c r="AC113" s="1">
         <v>17.161000000000001</v>
       </c>
@@ -12921,15 +13353,19 @@
       </c>
       <c r="AK113" s="1"/>
       <c r="AL113" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM113" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN113">
+        <f t="shared" si="24"/>
+        <v>16.235599999999998</v>
+      </c>
+    </row>
+    <row r="114" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>172</v>
       </c>
@@ -12962,11 +13398,11 @@
         <v>212.52799999999999</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-71.882999999999981</v>
       </c>
       <c r="M114" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>140.64500000000001</v>
       </c>
       <c r="N114" s="1"/>
@@ -12985,23 +13421,23 @@
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>28.129000000000001</v>
       </c>
       <c r="X114" s="5">
         <v>120</v>
       </c>
       <c r="Y114" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>120</v>
       </c>
       <c r="Z114" s="5"/>
       <c r="AA114" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.8579046535603823</v>
       </c>
       <c r="AB114" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.5918447154182518</v>
       </c>
       <c r="AC114" s="1">
@@ -13030,15 +13466,19 @@
       </c>
       <c r="AK114" s="1"/>
       <c r="AL114" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>120</v>
       </c>
       <c r="AM114" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN114">
+        <f t="shared" si="24"/>
+        <v>28.129000000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>173</v>
       </c>
@@ -13071,11 +13511,11 @@
         <v>134</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-92</v>
       </c>
       <c r="M115" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>42</v>
       </c>
       <c r="N115" s="1"/>
@@ -13090,7 +13530,7 @@
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>8.4</v>
       </c>
       <c r="X115" s="5">
@@ -13098,16 +13538,16 @@
         <v>48.2</v>
       </c>
       <c r="Y115" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>48.2</v>
       </c>
       <c r="Z115" s="5"/>
       <c r="AA115" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8</v>
       </c>
       <c r="AB115" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.2619047619047619</v>
       </c>
       <c r="AC115" s="1">
@@ -13136,15 +13576,19 @@
       </c>
       <c r="AK115" s="1"/>
       <c r="AL115" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="AM115" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN115">
+        <f t="shared" si="24"/>
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="116" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>174</v>
       </c>
@@ -13177,11 +13621,11 @@
         <v>5.2</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-3.8160000000000003</v>
       </c>
       <c r="M116" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1.3839999999999999</v>
       </c>
       <c r="N116" s="1"/>
@@ -13196,23 +13640,23 @@
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.27679999999999999</v>
       </c>
       <c r="X116" s="5"/>
       <c r="Y116" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z116" s="5"/>
       <c r="AA116" s="1">
-        <f t="shared" si="19"/>
-        <v>65.415462427745666</v>
-      </c>
-      <c r="AB116" s="1">
         <f t="shared" si="20"/>
         <v>65.415462427745666</v>
       </c>
+      <c r="AB116" s="1">
+        <f t="shared" si="21"/>
+        <v>65.415462427745666</v>
+      </c>
       <c r="AC116" s="1">
         <v>0.55199999999999994</v>
       </c>
@@ -13241,15 +13685,19 @@
         <v>74</v>
       </c>
       <c r="AL116" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM116" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN116">
+        <f t="shared" si="24"/>
+        <v>0.27679999999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>175</v>
       </c>
@@ -13282,11 +13730,11 @@
         <v>627</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-263</v>
       </c>
       <c r="M117" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>364</v>
       </c>
       <c r="N117" s="1"/>
@@ -13309,23 +13757,23 @@
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>72.8</v>
       </c>
       <c r="X117" s="5">
         <v>200</v>
       </c>
       <c r="Y117" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>200</v>
       </c>
       <c r="Z117" s="5"/>
       <c r="AA117" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.1411503324646759</v>
       </c>
       <c r="AB117" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.3938975852119286</v>
       </c>
       <c r="AC117" s="1">
@@ -13354,15 +13802,19 @@
       </c>
       <c r="AK117" s="1"/>
       <c r="AL117" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>56</v>
       </c>
       <c r="AM117" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN117">
+        <f t="shared" si="24"/>
+        <v>20.384</v>
+      </c>
+    </row>
+    <row r="118" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>176</v>
       </c>
@@ -13395,11 +13847,11 @@
         <v>150</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-154</v>
       </c>
       <c r="M118" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-4</v>
       </c>
       <c r="N118" s="1"/>
@@ -13418,23 +13870,23 @@
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-0.8</v>
       </c>
       <c r="X118" s="5">
         <v>150</v>
       </c>
       <c r="Y118" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>150</v>
       </c>
       <c r="Z118" s="5"/>
       <c r="AA118" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-364.65749999999997</v>
       </c>
       <c r="AB118" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-177.1575</v>
       </c>
       <c r="AC118" s="1">
@@ -13463,15 +13915,19 @@
       </c>
       <c r="AK118" s="1"/>
       <c r="AL118" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>42</v>
       </c>
       <c r="AM118" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN118">
+        <f t="shared" si="24"/>
+        <v>-0.22400000000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>177</v>
       </c>
@@ -13504,11 +13960,11 @@
         <v>924</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-422</v>
       </c>
       <c r="M119" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>502</v>
       </c>
       <c r="N119" s="1"/>
@@ -13527,23 +13983,23 @@
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>100.4</v>
       </c>
       <c r="X119" s="5">
         <v>300</v>
       </c>
       <c r="Y119" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>300</v>
       </c>
       <c r="Z119" s="5"/>
       <c r="AA119" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.5229083665338639</v>
       </c>
       <c r="AB119" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.534860557768924</v>
       </c>
       <c r="AC119" s="1">
@@ -13572,15 +14028,19 @@
       </c>
       <c r="AK119" s="1"/>
       <c r="AL119" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>84</v>
       </c>
       <c r="AM119" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN119">
+        <f t="shared" si="24"/>
+        <v>28.112000000000005</v>
+      </c>
+    </row>
+    <row r="120" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>178</v>
       </c>
@@ -13613,11 +14073,11 @@
         <v>327</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-163</v>
       </c>
       <c r="M120" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>164</v>
       </c>
       <c r="N120" s="1"/>
@@ -13632,23 +14092,23 @@
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32.799999999999997</v>
       </c>
       <c r="X120" s="5"/>
       <c r="Y120" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z120" s="5"/>
       <c r="AA120" s="1">
-        <f t="shared" si="19"/>
-        <v>27.476219512195126</v>
-      </c>
-      <c r="AB120" s="1">
         <f t="shared" si="20"/>
         <v>27.476219512195126</v>
       </c>
+      <c r="AB120" s="1">
+        <f t="shared" si="21"/>
+        <v>27.476219512195126</v>
+      </c>
       <c r="AC120" s="1">
         <v>20.2</v>
       </c>
@@ -13677,15 +14137,19 @@
         <v>179</v>
       </c>
       <c r="AL120" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM120" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN120">
+        <f t="shared" si="24"/>
+        <v>2.9519999999999995</v>
+      </c>
+    </row>
+    <row r="121" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
         <v>180</v>
       </c>
@@ -13712,11 +14176,11 @@
       <c r="J121" s="9"/>
       <c r="K121" s="9"/>
       <c r="L121" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M121" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N121" s="9"/>
@@ -13731,23 +14195,23 @@
       <c r="U121" s="9"/>
       <c r="V121" s="9"/>
       <c r="W121" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X121" s="11"/>
       <c r="Y121" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z121" s="5"/>
       <c r="AA121" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB121" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB121" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC121" s="9">
         <v>0</v>
       </c>
@@ -13774,15 +14238,19 @@
       </c>
       <c r="AK121" s="9"/>
       <c r="AL121" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM121" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN121">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>181</v>
       </c>
@@ -13813,11 +14281,11 @@
         <v>50</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-0.14699999999999847</v>
       </c>
       <c r="M122" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>49.853000000000002</v>
       </c>
       <c r="N122" s="1"/>
@@ -13832,7 +14300,7 @@
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>9.970600000000001</v>
       </c>
       <c r="X122" s="5">
@@ -13840,16 +14308,16 @@
         <v>51.726600000000005</v>
       </c>
       <c r="Y122" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>51.726600000000005</v>
       </c>
       <c r="Z122" s="5"/>
       <c r="AA122" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11</v>
       </c>
       <c r="AB122" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.8120875373598375</v>
       </c>
       <c r="AC122" s="1">
@@ -13878,15 +14346,19 @@
       </c>
       <c r="AK122" s="1"/>
       <c r="AL122" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>52</v>
       </c>
       <c r="AM122" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN122">
+        <f t="shared" si="24"/>
+        <v>9.970600000000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>182</v>
       </c>
@@ -13917,11 +14389,11 @@
         <v>17.5</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-5.6999999999998607E-2</v>
       </c>
       <c r="M123" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>17.443000000000001</v>
       </c>
       <c r="N123" s="1"/>
@@ -13936,7 +14408,7 @@
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>3.4886000000000004</v>
       </c>
       <c r="X123" s="5">
@@ -13944,16 +14416,16 @@
         <v>17.1416</v>
       </c>
       <c r="Y123" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>17.1416</v>
       </c>
       <c r="Z123" s="5"/>
       <c r="AA123" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.999999999999998</v>
       </c>
       <c r="AB123" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.0863956888149966</v>
       </c>
       <c r="AC123" s="1">
@@ -13982,15 +14454,19 @@
       </c>
       <c r="AK123" s="1"/>
       <c r="AL123" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>17</v>
       </c>
       <c r="AM123" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN123">
+        <f t="shared" si="24"/>
+        <v>3.4886000000000004</v>
+      </c>
+    </row>
+    <row r="124" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>183</v>
       </c>
@@ -14021,11 +14497,11 @@
         <v>193</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M124" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>193</v>
       </c>
       <c r="N124" s="1"/>
@@ -14040,23 +14516,23 @@
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>38.6</v>
       </c>
       <c r="X124" s="5"/>
       <c r="Y124" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z124" s="5"/>
       <c r="AA124" s="1">
-        <f t="shared" si="19"/>
-        <v>13.756476683937823</v>
-      </c>
-      <c r="AB124" s="1">
         <f t="shared" si="20"/>
         <v>13.756476683937823</v>
       </c>
+      <c r="AB124" s="1">
+        <f t="shared" si="21"/>
+        <v>13.756476683937823</v>
+      </c>
       <c r="AC124" s="1">
         <v>11</v>
       </c>
@@ -14085,15 +14561,19 @@
         <v>184</v>
       </c>
       <c r="AL124" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM124" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN124">
+        <f t="shared" si="24"/>
+        <v>3.4740000000000002</v>
+      </c>
+    </row>
+    <row r="125" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>185</v>
       </c>
@@ -14126,11 +14606,11 @@
         <v>193</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-2</v>
       </c>
       <c r="M125" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>191</v>
       </c>
       <c r="N125" s="1"/>
@@ -14145,23 +14625,23 @@
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>38.200000000000003</v>
       </c>
       <c r="X125" s="5"/>
       <c r="Y125" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z125" s="5"/>
       <c r="AA125" s="1">
-        <f t="shared" si="19"/>
-        <v>16.282722513089006</v>
-      </c>
-      <c r="AB125" s="1">
         <f t="shared" si="20"/>
         <v>16.282722513089006</v>
       </c>
+      <c r="AB125" s="1">
+        <f t="shared" si="21"/>
+        <v>16.282722513089006</v>
+      </c>
       <c r="AC125" s="1">
         <v>16.399999999999999</v>
       </c>
@@ -14190,15 +14670,19 @@
         <v>157</v>
       </c>
       <c r="AL125" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM125" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN125">
+        <f t="shared" si="24"/>
+        <v>3.4380000000000002</v>
+      </c>
+    </row>
+    <row r="126" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>186</v>
       </c>
@@ -14231,11 +14715,11 @@
         <v>126.88200000000001</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-6.8070000000000022</v>
       </c>
       <c r="M126" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>120.075</v>
       </c>
       <c r="N126" s="1"/>
@@ -14250,23 +14734,23 @@
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>24.015000000000001</v>
       </c>
       <c r="X126" s="5"/>
       <c r="Y126" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z126" s="5"/>
       <c r="AA126" s="1">
-        <f t="shared" si="19"/>
-        <v>10.779512804497189</v>
-      </c>
-      <c r="AB126" s="1">
         <f t="shared" si="20"/>
         <v>10.779512804497189</v>
       </c>
+      <c r="AB126" s="1">
+        <f t="shared" si="21"/>
+        <v>10.779512804497189</v>
+      </c>
       <c r="AC126" s="1">
         <v>15.4374</v>
       </c>
@@ -14295,15 +14779,19 @@
         <v>187</v>
       </c>
       <c r="AL126" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM126" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN126">
+        <f t="shared" si="24"/>
+        <v>24.015000000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>188</v>
       </c>
@@ -14336,11 +14824,11 @@
         <v>608</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-40.842999999999961</v>
       </c>
       <c r="M127" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>567.15700000000004</v>
       </c>
       <c r="N127" s="1"/>
@@ -14355,23 +14843,23 @@
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>113.43140000000001</v>
       </c>
       <c r="X127" s="5"/>
       <c r="Y127" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z127" s="5"/>
       <c r="AA127" s="1">
-        <f t="shared" si="19"/>
-        <v>11.019603037606871</v>
-      </c>
-      <c r="AB127" s="1">
         <f t="shared" si="20"/>
         <v>11.019603037606871</v>
       </c>
+      <c r="AB127" s="1">
+        <f t="shared" si="21"/>
+        <v>11.019603037606871</v>
+      </c>
       <c r="AC127" s="1">
         <v>129.72380000000001</v>
       </c>
@@ -14398,15 +14886,19 @@
       </c>
       <c r="AK127" s="1"/>
       <c r="AL127" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM127" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN127">
+        <f t="shared" si="24"/>
+        <v>113.43140000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>189</v>
       </c>
@@ -14439,11 +14931,11 @@
         <v>81.962000000000003</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-7.171999999999997</v>
       </c>
       <c r="M128" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>74.790000000000006</v>
       </c>
       <c r="N128" s="1"/>
@@ -14458,7 +14950,7 @@
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>14.958000000000002</v>
       </c>
       <c r="X128" s="5">
@@ -14466,16 +14958,16 @@
         <v>52.993000000000009</v>
       </c>
       <c r="Y128" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>52.993000000000009</v>
       </c>
       <c r="Z128" s="5"/>
       <c r="AA128" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="AB128" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.4572135312207504</v>
       </c>
       <c r="AC128" s="1">
@@ -14506,15 +14998,19 @@
         <v>190</v>
       </c>
       <c r="AL128" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>53</v>
       </c>
       <c r="AM128" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN128">
+        <f t="shared" si="24"/>
+        <v>14.958000000000002</v>
+      </c>
+    </row>
+    <row r="129" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>61</v>
       </c>
@@ -14549,11 +15045,11 @@
         <v>972</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-57.974000000000046</v>
       </c>
       <c r="M129" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>914.02599999999995</v>
       </c>
       <c r="N129" s="1"/>
@@ -14572,23 +15068,23 @@
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>182.80519999999999</v>
       </c>
       <c r="X129" s="5"/>
       <c r="Y129" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z129" s="5"/>
       <c r="AA129" s="1">
-        <f t="shared" si="19"/>
-        <v>18.595599613577733</v>
-      </c>
-      <c r="AB129" s="1">
         <f t="shared" si="20"/>
         <v>18.595599613577733</v>
       </c>
+      <c r="AB129" s="1">
+        <f t="shared" si="21"/>
+        <v>18.595599613577733</v>
+      </c>
       <c r="AC129" s="1">
         <v>261.65699999999998</v>
       </c>
@@ -14615,15 +15111,19 @@
       </c>
       <c r="AK129" s="1"/>
       <c r="AL129" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM129" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN129">
+        <f t="shared" si="24"/>
+        <v>182.80519999999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>191</v>
       </c>
@@ -14654,11 +15154,11 @@
         <v>29</v>
       </c>
       <c r="L130" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-8</v>
       </c>
       <c r="M130" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>21</v>
       </c>
       <c r="N130" s="1"/>
@@ -14675,23 +15175,23 @@
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>4.2</v>
       </c>
       <c r="X130" s="5"/>
       <c r="Y130" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z130" s="5"/>
       <c r="AA130" s="1">
-        <f t="shared" si="19"/>
-        <v>22.142857142857142</v>
-      </c>
-      <c r="AB130" s="1">
         <f t="shared" si="20"/>
         <v>22.142857142857142</v>
       </c>
+      <c r="AB130" s="1">
+        <f t="shared" si="21"/>
+        <v>22.142857142857142</v>
+      </c>
       <c r="AC130" s="1">
         <v>6.2</v>
       </c>
@@ -14720,15 +15220,19 @@
         <v>192</v>
       </c>
       <c r="AL130" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM130" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN130">
+        <f t="shared" si="24"/>
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="131" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>193</v>
       </c>
@@ -14761,11 +15265,11 @@
         <v>9</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>9</v>
       </c>
       <c r="M131" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>18</v>
       </c>
       <c r="N131" s="1"/>
@@ -14780,23 +15284,23 @@
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>3.6</v>
       </c>
       <c r="X131" s="5"/>
       <c r="Y131" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z131" s="5"/>
       <c r="AA131" s="1">
-        <f t="shared" si="19"/>
-        <v>23.611111111111111</v>
-      </c>
-      <c r="AB131" s="1">
         <f t="shared" si="20"/>
         <v>23.611111111111111</v>
       </c>
+      <c r="AB131" s="1">
+        <f t="shared" si="21"/>
+        <v>23.611111111111111</v>
+      </c>
       <c r="AC131" s="1">
         <v>7.6</v>
       </c>
@@ -14825,15 +15329,19 @@
         <v>192</v>
       </c>
       <c r="AL131" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM131" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN131">
+        <f t="shared" si="24"/>
+        <v>1.1700000000000002</v>
+      </c>
+    </row>
+    <row r="132" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>194</v>
       </c>
@@ -14864,11 +15372,11 @@
         <v>56</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-7</v>
       </c>
       <c r="M132" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>49</v>
       </c>
       <c r="N132" s="1"/>
@@ -14883,7 +15391,7 @@
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="X132" s="5">
@@ -14891,16 +15399,16 @@
         <v>34.800000000000011</v>
       </c>
       <c r="Y132" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>34.800000000000011</v>
       </c>
       <c r="Z132" s="5"/>
       <c r="AA132" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11</v>
       </c>
       <c r="AB132" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7.4489795918367339</v>
       </c>
       <c r="AC132" s="1">
@@ -14931,15 +15439,19 @@
         <v>192</v>
       </c>
       <c r="AL132" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="AM132" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN132">
+        <f t="shared" si="24"/>
+        <v>2.4500000000000002</v>
+      </c>
+    </row>
+    <row r="133" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>195</v>
       </c>
@@ -14972,11 +15484,11 @@
         <v>189</v>
       </c>
       <c r="L133" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-192</v>
       </c>
       <c r="M133" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-3</v>
       </c>
       <c r="N133" s="1"/>
@@ -14995,23 +15507,23 @@
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-0.6</v>
       </c>
       <c r="X133" s="5"/>
       <c r="Y133" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z133" s="5"/>
       <c r="AA133" s="1">
-        <f t="shared" si="19"/>
-        <v>-133.33333333333334</v>
-      </c>
-      <c r="AB133" s="1">
         <f t="shared" si="20"/>
         <v>-133.33333333333334</v>
       </c>
+      <c r="AB133" s="1">
+        <f t="shared" si="21"/>
+        <v>-133.33333333333334</v>
+      </c>
       <c r="AC133" s="1">
         <v>13.2</v>
       </c>
@@ -15038,15 +15550,19 @@
       </c>
       <c r="AK133" s="1"/>
       <c r="AL133" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AM133" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN133">
+        <f t="shared" si="24"/>
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>196</v>
       </c>
@@ -15075,11 +15591,11 @@
         <v>14</v>
       </c>
       <c r="L134" s="1">
-        <f t="shared" ref="L134:L138" si="26">E134-K134</f>
+        <f t="shared" ref="L134:L138" si="28">E134-K134</f>
         <v>-14</v>
       </c>
       <c r="M134" s="1">
-        <f t="shared" ref="M134:M138" si="27">E134-N134</f>
+        <f t="shared" ref="M134:M138" si="29">E134-N134</f>
         <v>0</v>
       </c>
       <c r="N134" s="1"/>
@@ -15098,25 +15614,25 @@
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X134" s="5">
         <v>50</v>
       </c>
       <c r="Y134" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>50</v>
       </c>
       <c r="Z134" s="5"/>
       <c r="AA134" s="1" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB134" s="1" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AB134" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC134" s="1">
         <v>0.4</v>
       </c>
@@ -15143,15 +15659,19 @@
       </c>
       <c r="AK134" s="1"/>
       <c r="AL134" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="AM134" s="1">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN134">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>197</v>
       </c>
@@ -15184,11 +15704,11 @@
         <v>46.8</v>
       </c>
       <c r="L135" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-2.6159999999999997</v>
       </c>
       <c r="M135" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>44.183999999999997</v>
       </c>
       <c r="N135" s="1"/>
@@ -15203,21 +15723,21 @@
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>8.8368000000000002</v>
       </c>
       <c r="X135" s="5"/>
       <c r="Y135" s="5">
-        <f t="shared" ref="Y135:Y138" si="28">X135</f>
+        <f t="shared" ref="Y135:Y138" si="30">X135</f>
         <v>0</v>
       </c>
       <c r="Z135" s="5"/>
       <c r="AA135" s="1">
-        <f t="shared" ref="AA135:AA138" si="29">(F135+O135+P135+Q135+R135+S135+T135+Y135+V135+U135+Z135)/W135</f>
+        <f t="shared" ref="AA135:AA138" si="31">(F135+O135+P135+Q135+R135+S135+T135+Y135+V135+U135+Z135)/W135</f>
         <v>12.062533948940791</v>
       </c>
       <c r="AB135" s="1">
-        <f t="shared" ref="AB135:AB138" si="30">(F135+O135+P135+Q135+R135+S135+T135+U135+V135)/W135</f>
+        <f t="shared" ref="AB135:AB138" si="32">(F135+O135+P135+Q135+R135+S135+T135+U135+V135)/W135</f>
         <v>12.062533948940791</v>
       </c>
       <c r="AC135" s="1">
@@ -15246,15 +15766,19 @@
       </c>
       <c r="AK135" s="1"/>
       <c r="AL135" s="1">
-        <f t="shared" ref="AL135:AM138" si="31">ROUND(G135*Y135,0)</f>
+        <f t="shared" ref="AL135:AL138" si="33">ROUND(G135*Y135,0)</f>
         <v>0</v>
       </c>
       <c r="AM135" s="1">
-        <f t="shared" ref="AM135:AM138" si="32">ROUND(G135*Z135,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AM135:AM138" si="34">ROUND(G135*Z135,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN135">
+        <f t="shared" ref="AN135:AN138" si="35">W135*G135</f>
+        <v>8.8368000000000002</v>
+      </c>
+    </row>
+    <row r="136" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>198</v>
       </c>
@@ -15285,11 +15809,11 @@
         <v>40</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-40</v>
       </c>
       <c r="M136" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N136" s="1"/>
@@ -15308,21 +15832,21 @@
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X136" s="5"/>
       <c r="Y136" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z136" s="5"/>
       <c r="AA136" s="1" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB136" s="1" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC136" s="1">
@@ -15353,15 +15877,19 @@
         <v>65</v>
       </c>
       <c r="AL136" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AM136" s="1">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AN136">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>199</v>
       </c>
@@ -15394,11 +15922,11 @@
         <v>43</v>
       </c>
       <c r="L137" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-8</v>
       </c>
       <c r="M137" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>35</v>
       </c>
       <c r="N137" s="1"/>
@@ -15413,21 +15941,21 @@
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>7</v>
       </c>
       <c r="X137" s="5"/>
       <c r="Y137" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z137" s="5"/>
       <c r="AA137" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>22.285714285714295</v>
       </c>
       <c r="AB137" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>22.285714285714295</v>
       </c>
       <c r="AC137" s="1">
@@ -15456,15 +15984,19 @@
       </c>
       <c r="AK137" s="1"/>
       <c r="AL137" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AM137" s="1">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AN137">
+        <f t="shared" si="35"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="138" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
         <v>200</v>
       </c>
@@ -15497,11 +16029,11 @@
         <v>17</v>
       </c>
       <c r="L138" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-4</v>
       </c>
       <c r="M138" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>13</v>
       </c>
       <c r="N138" s="9"/>
@@ -15516,21 +16048,21 @@
       <c r="U138" s="9"/>
       <c r="V138" s="9"/>
       <c r="W138" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2.6</v>
       </c>
       <c r="X138" s="11"/>
       <c r="Y138" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z138" s="5"/>
       <c r="AA138" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>12.307692307692307</v>
       </c>
       <c r="AB138" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>12.307692307692307</v>
       </c>
       <c r="AC138" s="9">
@@ -15559,15 +16091,19 @@
       </c>
       <c r="AK138" s="9"/>
       <c r="AL138" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AM138" s="1">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:39" x14ac:dyDescent="0.25">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AN138">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -15608,7 +16144,7 @@
       <c r="AL139" s="1"/>
       <c r="AM139" s="1"/>
     </row>
-    <row r="140" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -15649,7 +16185,7 @@
       <c r="AL140" s="1"/>
       <c r="AM140" s="1"/>
     </row>
-    <row r="141" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -15690,7 +16226,7 @@
       <c r="AL141" s="1"/>
       <c r="AM141" s="1"/>
     </row>
-    <row r="142" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -15731,7 +16267,7 @@
       <c r="AL142" s="1"/>
       <c r="AM142" s="1"/>
     </row>
-    <row r="143" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -15772,7 +16308,7 @@
       <c r="AL143" s="1"/>
       <c r="AM143" s="1"/>
     </row>
-    <row r="144" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
